--- a/docs/project/drafts/mentor-questions-2026-10.xlsx
+++ b/docs/project/drafts/mentor-questions-2026-10.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -519,7 +519,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Заказчик — Hivetrace, но пока не очень понятен формат. Как должен работать модуль: как промежуточный сервис между пользователем и LLM, как отдельный сервис, который вызывают по API, или как-то иначе?</t>
+          <t>Для чего разрабатываем модуль: где он будет применяться — только в чат-ботах или ещё где-то (например, в AI-агентах, внутренних ассистентах, при обработке писем или документов)?</t>
         </is>
       </c>
       <c r="C5" s="6" t="n"/>
@@ -530,7 +530,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Смотрим только на данные самого пользователя или на третьих лиц, которых он упоминает (маму, коллегу и т.п.), тоже?</t>
+          <t>Заказчик — Hivetrace, но пока не очень понятен формат. Как должен работать модуль: как промежуточный сервис между пользователем и LLM, как отдельный сервис, который вызывают по API, или как-то иначе?</t>
         </is>
       </c>
       <c r="C6" s="6" t="n"/>
@@ -541,7 +541,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Мы исходим из того, что модуль работает полностью локально, без внешних API. Это так? И есть ли ориентир, на каком железе он должен работать и сколько времени можно тратить на одно сообщение?</t>
+          <t>Как анализировать сессию: каждый раз целиком всю историю или итеративно — пришло новое сообщение, обновили накопленное состояние? Есть ли ограничение на длину сессии?</t>
         </is>
       </c>
       <c r="C7" s="6" t="n"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Что модуль должен отдавать на выходе: просто флаг «тут ПДн», оценку риска или подробнее — кто упомянут и что о нём известно? И что происходит дальше: сообщение блокируется, маскируется, пользователя предупреждают?</t>
+          <t>Смотрим только на данные самого пользователя или на третьих лиц, которых он упоминает (маму, коллегу и т.п.), тоже?</t>
         </is>
       </c>
       <c r="C8" s="6" t="n"/>
@@ -563,7 +563,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Что хуже: пропустить утечку или поднять ложную тревогу?</t>
+          <t>Мы исходим из того, что модуль работает полностью локально, без внешних API. Это так? И есть ли ориентир, на каком железе он должен работать и сколько времени можно тратить на одно сообщение?</t>
         </is>
       </c>
       <c r="C9" s="6" t="n"/>
@@ -574,7 +574,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Достаточно ли только русского языка?</t>
+          <t>Что модуль должен отдавать на выходе: просто флаг «тут ПДн», оценку риска или подробнее — кто упомянут и что о нём известно? И что происходит дальше: сообщение блокируется, маскируется, пользователя предупреждают?</t>
         </is>
       </c>
       <c r="C10" s="6" t="n"/>
@@ -585,10 +585,32 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
+          <t>Что хуже: пропустить утечку или поднять ложную тревогу?</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n"/>
+    </row>
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Достаточно ли только русского языка?</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n"/>
+    </row>
+    <row r="13" ht="60" customHeight="1">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
           <t>Что вы хотите увидеть на первом чекпоинте 5 ноября: обзор и возможные направления или уже выбранное направление и план MVP?</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
